--- a/data/trans_orig/IP32-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP32-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>15685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>124963</t>
+          <t>124305</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134034</t>
+          <t>133382</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134085</t>
+          <t>133854</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145785</t>
+          <t>145866</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>262987</t>
+          <t>262444</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>276990</t>
+          <t>276839</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>12159</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21105</t>
+          <t>21263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19388</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26717</t>
+          <t>26843</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174524</t>
+          <t>175357</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>185682</t>
+          <t>185737</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>182875</t>
+          <t>183069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>196888</t>
+          <t>197043</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>361838</t>
+          <t>362585</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>379887</t>
+          <t>380672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17711</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>28366</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11251</t>
+          <t>11265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17154</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114639</t>
+          <t>115275</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126710</t>
+          <t>126863</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>126020</t>
+          <t>126352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138667</t>
+          <t>138904</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>246751</t>
+          <t>245440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>262302</t>
+          <t>262631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13824</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27637</t>
+          <t>28777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25948</t>
+          <t>26670</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>22521</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>24499</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43463</t>
+          <t>43887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>173235</t>
+          <t>172985</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>189861</t>
+          <t>190099</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>171656</t>
+          <t>171444</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>187389</t>
+          <t>187129</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>351718</t>
+          <t>350031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>373675</t>
+          <t>373410</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41421</t>
+          <t>41538</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>24984</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42478</t>
+          <t>42657</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51763</t>
+          <t>53586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78306</t>
+          <t>78284</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41576</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>31907</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52389</t>
+          <t>51429</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>60904</t>
+          <t>61271</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>87207</t>
+          <t>87948</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>602637</t>
+          <t>601674</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>625959</t>
+          <t>626517</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>632968</t>
+          <t>632812</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>659522</t>
+          <t>658334</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1242459</t>
+          <t>1243199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1278423</t>
+          <t>1278122</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>11509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>987</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125353</t>
+          <t>125541</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136160</t>
+          <t>136685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>148059</t>
+          <t>147792</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154050</t>
+          <t>154054</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>277424</t>
+          <t>276940</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>289189</t>
+          <t>288947</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13726</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18822</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>190292</t>
+          <t>189283</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>200804</t>
+          <t>200456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204409</t>
+          <t>204169</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>216822</t>
+          <t>216891</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>398926</t>
+          <t>398913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>414917</t>
+          <t>415499</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139622</t>
+          <t>138884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150379</t>
+          <t>150332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145654</t>
+          <t>144971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>158516</t>
+          <t>158163</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289219</t>
+          <t>289502</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>305937</t>
+          <t>305899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>20012</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29122</t>
+          <t>28773</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>191103</t>
+          <t>191030</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>203492</t>
+          <t>203875</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>189258</t>
+          <t>187772</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202403</t>
+          <t>201944</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385353</t>
+          <t>385998</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>403666</t>
+          <t>403894</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37041</t>
+          <t>36547</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19118</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39897</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41072</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69352</t>
+          <t>68709</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>16522</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32504</t>
+          <t>32196</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>661289</t>
+          <t>661036</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>683636</t>
+          <t>682673</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>700794</t>
+          <t>701929</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>723993</t>
+          <t>724527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1369732</t>
+          <t>1371707</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1402025</t>
+          <t>1403888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12526</t>
+          <t>12572</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125444</t>
+          <t>126862</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132983</t>
+          <t>132991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>138445</t>
+          <t>138639</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146642</t>
+          <t>146407</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>267856</t>
+          <t>267197</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>278449</t>
+          <t>278167</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23066</t>
+          <t>23831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>185052</t>
+          <t>186471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>198341</t>
+          <t>198958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207867</t>
+          <t>207516</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>218434</t>
+          <t>218554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>398849</t>
+          <t>398600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>415089</t>
+          <t>415412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143736</t>
+          <t>143267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152711</t>
+          <t>152658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159498</t>
+          <t>159285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>307844</t>
+          <t>307670</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318343</t>
+          <t>318196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>13611</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195824</t>
+          <t>195525</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>204877</t>
+          <t>204777</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>194628</t>
+          <t>194372</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203211</t>
+          <t>203034</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>393797</t>
+          <t>393992</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>406507</t>
+          <t>406266</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25546</t>
+          <t>24565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42405</t>
+          <t>42741</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28023</t>
+          <t>28032</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>665699</t>
+          <t>665910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>684384</t>
+          <t>683685</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>713216</t>
+          <t>713081</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>730234</t>
+          <t>729719</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1384679</t>
+          <t>1384601</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1411031</t>
+          <t>1409256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27671</t>
+          <t>31523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>30232</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116541</t>
+          <t>116360</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109968</t>
+          <t>106755</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>138445</t>
+          <t>138227</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>223972</t>
+          <t>226487</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>255519</t>
+          <t>255145</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>178884</t>
+          <t>178526</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187732</t>
+          <t>187800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>243015</t>
+          <t>243149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>251833</t>
+          <t>251769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>426079</t>
+          <t>425787</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>438114</t>
+          <t>438170</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20005</t>
+          <t>17915</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13866</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22785</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10197</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167593</t>
+          <t>170288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186457</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170575</t>
+          <t>170917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>182273</t>
+          <t>182139</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>346761</t>
+          <t>345710</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366202</t>
+          <t>366448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>500</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>153825</t>
+          <t>154012</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>163647</t>
+          <t>163372</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>174723</t>
+          <t>175094</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>179984</t>
+          <t>180046</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>331888</t>
+          <t>331743</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>342693</t>
+          <t>342317</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26582</t>
+          <t>27559</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>42390</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>54243</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>629554</t>
+          <t>630853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>650883</t>
+          <t>650820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>715563</t>
+          <t>714587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>745770</t>
+          <t>745205</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1354823</t>
+          <t>1357004</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1391371</t>
+          <t>1391987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
